--- a/テーブル.xlsx
+++ b/テーブル.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fajie\tool\work\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fajie\tool\csvToExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D04D4972-FEBB-4343-A324-448A4596DE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D247483-F9A3-4D28-876B-98BBEDC2C2E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テーブル" sheetId="1" r:id="rId1"/>
@@ -36,9 +36,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
   <si>
-    <t>取得SQL</t>
-  </si>
-  <si>
     <t>現</t>
   </si>
   <si>
@@ -61,10 +58,6 @@
   </si>
   <si>
     <t>打鍵後</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>SELECT * FROM テーブル名</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -102,6 +95,20 @@
   </si>
   <si>
     <t>日期</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>取得SQL(現)</t>
+    <rPh sb="6" eb="7">
+      <t>ゲン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>取得SQL(新)</t>
+    <rPh sb="6" eb="7">
+      <t>シン</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -799,7 +806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q38"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="18" width="12" customWidth="1"/>
@@ -807,64 +814,48 @@
   <sheetData>
     <row r="1" spans="1:17" s="18" customFormat="1" ht="14" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="6"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="8"/>
-    </row>
-    <row r="5" spans="1:17" ht="18.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="10"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B6" s="25"/>
-      <c r="C6" s="9"/>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="6"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="8"/>
+    </row>
+    <row r="6" spans="1:17" ht="18.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>9</v>
+      </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -880,1305 +871,1325 @@
       <c r="P6" s="3"/>
       <c r="Q6" s="10"/>
     </row>
-    <row r="7" spans="1:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="26"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="13"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B8" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="16"/>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B7" s="25"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="10"/>
+    </row>
+    <row r="8" spans="1:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="26"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="13"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B9" s="22"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="10"/>
-    </row>
-    <row r="10" spans="1:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="23"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="13"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B11" t="str">
-        <f>IF(COUNTIF(C11:W11,FALSE)&gt;0,"差分あり","差分なし")</f>
-        <v>差分あり</v>
-      </c>
-      <c r="C11" s="5" t="b">
-        <f>IF(AND(C5="",C8=""),"",EXACT(C5,C8))</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="5" t="str">
-        <f t="shared" ref="D11:Q11" si="0">IF(AND(D5="",D8=""),"",EXACT(D5,D8))</f>
-        <v/>
-      </c>
-      <c r="E11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Q11" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="B9" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="16"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B10" s="22"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="10"/>
+    </row>
+    <row r="11" spans="1:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="23"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="13"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12" t="str">
-        <f t="shared" ref="B12:B13" si="1">IF(COUNTIF(C12:W12,FALSE)&gt;0,"差分あり","差分なし")</f>
-        <v>差分なし</v>
-      </c>
-      <c r="C12" s="5" t="str">
-        <f t="shared" ref="C12:Q12" si="2">IF(AND(C6="",C9=""),"",EXACT(C6,C9))</f>
-        <v/>
+        <f>IF(COUNTIF(C12:W12,FALSE)&gt;0,"差分あり","差分なし")</f>
+        <v>差分あり</v>
+      </c>
+      <c r="C12" s="5" t="b">
+        <f>IF(AND(C6="",C9=""),"",EXACT(C6,C9))</f>
+        <v>0</v>
       </c>
       <c r="D12" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="D12:Q12" si="0">IF(AND(D6="",D9=""),"",EXACT(D6,D9))</f>
         <v/>
       </c>
       <c r="E12" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="F12" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="G12" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="H12" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I12" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J12" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="K12" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="L12" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M12" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="N12" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="O12" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="P12" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Q12" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" t="str">
+        <f t="shared" ref="B13:B14" si="1">IF(COUNTIF(C13:W13,FALSE)&gt;0,"差分あり","差分なし")</f>
+        <v>差分なし</v>
+      </c>
+      <c r="C13" s="5" t="str">
+        <f t="shared" ref="C13:Q13" si="2">IF(AND(C7="",C10=""),"",EXACT(C7,C10))</f>
+        <v/>
+      </c>
+      <c r="D13" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="E13" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F13" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="G13" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H13" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="I13" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J13" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K13" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L13" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M13" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="N13" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O13" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="P13" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="Q13" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B14" t="str">
         <f t="shared" si="1"/>
         <v>差分なし</v>
       </c>
-      <c r="C13" s="5" t="str">
-        <f t="shared" ref="C13:Q13" si="3">IF(AND(C7="",C10=""),"",EXACT(C7,C10))</f>
-        <v/>
-      </c>
-      <c r="D13" s="5" t="str">
+      <c r="C14" s="5" t="str">
+        <f t="shared" ref="C14:Q14" si="3">IF(AND(C8="",C11=""),"",EXACT(C8,C11))</f>
+        <v/>
+      </c>
+      <c r="D14" s="5" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="E13" s="5" t="str">
+      <c r="E14" s="5" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="F13" s="5" t="str">
+      <c r="F14" s="5" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="G13" s="5" t="str">
+      <c r="G14" s="5" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="H13" s="5" t="str">
+      <c r="H14" s="5" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I13" s="5" t="str">
+      <c r="I14" s="5" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J13" s="5" t="str">
+      <c r="J14" s="5" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K13" s="5" t="str">
+      <c r="K14" s="5" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L13" s="5" t="str">
+      <c r="L14" s="5" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M13" s="5" t="str">
+      <c r="M14" s="5" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="N13" s="5" t="str">
+      <c r="N14" s="5" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O13" s="5" t="str">
+      <c r="O14" s="5" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P13" s="5" t="str">
+      <c r="P14" s="5" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q13" s="5" t="str">
+      <c r="Q14" s="5" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
+    <row r="16" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B20" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="C16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B18" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3" t="str">
-        <f t="shared" ref="D18:Q18" si="4">IF(AND(D5="",D8=""),"",EXACT(D5,D8))</f>
-        <v/>
-      </c>
-      <c r="E18" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="F18" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G18" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H18" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I18" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J18" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K18" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="L18" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M18" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="N18" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="O18" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P18" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="Q18" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B19" s="25"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3" t="str">
-        <f t="shared" ref="D19:Q19" si="5">IF(AND(D6="",D9=""),"",EXACT(D6,D9))</f>
-        <v/>
-      </c>
-      <c r="E19" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="F19" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G19" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H19" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="I19" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="J19" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K19" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="L19" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="M19" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N19" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="O19" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="P19" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Q19" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="26"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3" t="str">
-        <f t="shared" ref="D20:Q20" si="6">IF(AND(D7="",D10=""),"",EXACT(D7,D10))</f>
+        <f t="shared" ref="D20:Q20" si="4">IF(AND(D6="",D9=""),"",EXACT(D6,D9))</f>
         <v/>
       </c>
       <c r="E20" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="F20" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="G20" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="H20" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I20" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J20" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K20" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="L20" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="M20" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N20" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O20" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P20" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="Q20" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B21" s="21" t="s">
-        <v>2</v>
-      </c>
+      <c r="B21" s="25"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3" t="str">
-        <f t="shared" ref="D21:Q21" si="7">IF(AND(D8="",D11=""),"",EXACT(D8,D11))</f>
+        <f t="shared" ref="D21:Q21" si="5">IF(AND(D7="",D10=""),"",EXACT(D7,D10))</f>
         <v/>
       </c>
       <c r="E21" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="F21" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G21" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H21" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="I21" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J21" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="K21" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="L21" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="M21" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="N21" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O21" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P21" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="Q21" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="26"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3" t="str">
+        <f t="shared" ref="D22:Q22" si="6">IF(AND(D8="",D11=""),"",EXACT(D8,D11))</f>
+        <v/>
+      </c>
+      <c r="E22" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="F22" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="G22" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="H22" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I22" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="J22" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K22" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="L22" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="M22" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="N22" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="O22" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="P22" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="Q22" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B23" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3" t="str">
+        <f t="shared" ref="D23:Q23" si="7">IF(AND(D9="",D12=""),"",EXACT(D9,D12))</f>
+        <v/>
+      </c>
+      <c r="E23" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="F21" s="3" t="str">
+      <c r="F23" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="G21" s="3" t="str">
+      <c r="G23" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="H21" s="3" t="str">
+      <c r="H23" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="I21" s="3" t="str">
+      <c r="I23" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J21" s="3" t="str">
+      <c r="J23" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="K21" s="3" t="str">
+      <c r="K23" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="L21" s="3" t="str">
+      <c r="L23" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="M21" s="3" t="str">
+      <c r="M23" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N21" s="3" t="str">
+      <c r="N23" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="O21" s="3" t="str">
+      <c r="O23" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P21" s="3" t="str">
+      <c r="P23" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q21" s="3" t="str">
+      <c r="Q23" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B22" s="22"/>
-      <c r="C22" s="3" t="str">
-        <f>IF(AND(C9="",C12=""),"",EXACT(C9,C12))</f>
-        <v/>
-      </c>
-      <c r="D22" s="3" t="str">
-        <f t="shared" ref="D22:Q22" si="8">IF(AND(D9="",D12=""),"",EXACT(D9,D12))</f>
-        <v/>
-      </c>
-      <c r="E22" s="3" t="str">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B24" s="22"/>
+      <c r="C24" s="3" t="str">
+        <f>IF(AND(C10="",C13=""),"",EXACT(C10,C13))</f>
+        <v/>
+      </c>
+      <c r="D24" s="3" t="str">
+        <f t="shared" ref="D24:Q24" si="8">IF(AND(D10="",D13=""),"",EXACT(D10,D13))</f>
+        <v/>
+      </c>
+      <c r="E24" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="F22" s="3" t="str">
+      <c r="F24" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G22" s="3" t="str">
+      <c r="G24" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="H22" s="3" t="str">
+      <c r="H24" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="I22" s="3" t="str">
+      <c r="I24" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J22" s="3" t="str">
+      <c r="J24" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="K22" s="3" t="str">
+      <c r="K24" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="L22" s="3" t="str">
+      <c r="L24" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="M22" s="3" t="str">
+      <c r="M24" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="N22" s="3" t="str">
+      <c r="N24" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="O22" s="3" t="str">
+      <c r="O24" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="P22" s="3" t="str">
+      <c r="P24" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="Q22" s="3" t="str">
+      <c r="Q24" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="23" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="23"/>
-      <c r="C23" s="3" t="str">
-        <f>IF(AND(C10="",C13=""),"",EXACT(C10,C13))</f>
-        <v/>
-      </c>
-      <c r="D23" s="3" t="str">
-        <f t="shared" ref="D23:Q23" si="9">IF(AND(D10="",D13=""),"",EXACT(D10,D13))</f>
-        <v/>
-      </c>
-      <c r="E23" s="3" t="str">
+    <row r="25" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="23"/>
+      <c r="C25" s="3" t="str">
+        <f>IF(AND(C11="",C14=""),"",EXACT(C11,C14))</f>
+        <v/>
+      </c>
+      <c r="D25" s="3" t="str">
+        <f t="shared" ref="D25:Q25" si="9">IF(AND(D11="",D14=""),"",EXACT(D11,D14))</f>
+        <v/>
+      </c>
+      <c r="E25" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="F23" s="3" t="str">
+      <c r="F25" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="G23" s="3" t="str">
+      <c r="G25" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="H23" s="3" t="str">
+      <c r="H25" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="I23" s="3" t="str">
+      <c r="I25" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J23" s="3" t="str">
+      <c r="J25" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="K23" s="3" t="str">
+      <c r="K25" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="L23" s="3" t="str">
+      <c r="L25" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="M23" s="3" t="str">
+      <c r="M25" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="N23" s="3" t="str">
+      <c r="N25" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O23" s="3" t="str">
+      <c r="O25" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="P23" s="3" t="str">
+      <c r="P25" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="Q23" s="3" t="str">
+      <c r="Q25" s="3" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B24" t="str">
-        <f>IF(COUNTIF(C24:W24,FALSE)&gt;0,"差分あり","差分なし")</f>
-        <v>差分なし</v>
-      </c>
-      <c r="C24" s="5" t="str">
-        <f>IF(AND(C18="",C21=""),"",EXACT(C18,C21))</f>
-        <v/>
-      </c>
-      <c r="D24" s="5" t="str">
-        <f t="shared" ref="D24:Q24" si="10">IF(AND(D18="",D21=""),"",EXACT(D18,D21))</f>
-        <v/>
-      </c>
-      <c r="E24" s="5" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F24" s="5" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="G24" s="5" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H24" s="5" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="I24" s="5" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J24" s="5" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="K24" s="5" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="L24" s="5" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="M24" s="5" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="N24" s="5" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O24" s="5" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="P24" s="5" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="Q24" s="5" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B25" t="str">
-        <f t="shared" ref="B25:B26" si="11">IF(COUNTIF(C25:W25,FALSE)&gt;0,"差分あり","差分なし")</f>
-        <v>差分なし</v>
-      </c>
-      <c r="C25" s="5" t="str">
-        <f t="shared" ref="C25:Q25" si="12">IF(AND(C19="",C22=""),"",EXACT(C19,C22))</f>
-        <v/>
-      </c>
-      <c r="D25" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="E25" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="F25" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="G25" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H25" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="I25" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J25" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="K25" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="L25" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="M25" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="N25" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="O25" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P25" s="5" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="Q25" s="5" t="str">
-        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B26" t="str">
+        <f>IF(COUNTIF(C26:W26,FALSE)&gt;0,"差分あり","差分なし")</f>
+        <v>差分なし</v>
+      </c>
+      <c r="C26" s="5" t="str">
+        <f>IF(AND(C20="",C23=""),"",EXACT(C20,C23))</f>
+        <v/>
+      </c>
+      <c r="D26" s="5" t="str">
+        <f t="shared" ref="D26:Q26" si="10">IF(AND(D20="",D23=""),"",EXACT(D20,D23))</f>
+        <v/>
+      </c>
+      <c r="E26" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="F26" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="G26" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H26" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="I26" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="J26" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="K26" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L26" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="M26" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="N26" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="O26" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="P26" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="Q26" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B27" t="str">
+        <f t="shared" ref="B27:B28" si="11">IF(COUNTIF(C27:W27,FALSE)&gt;0,"差分あり","差分なし")</f>
+        <v>差分なし</v>
+      </c>
+      <c r="C27" s="5" t="str">
+        <f t="shared" ref="C27:Q27" si="12">IF(AND(C21="",C24=""),"",EXACT(C21,C24))</f>
+        <v/>
+      </c>
+      <c r="D27" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="E27" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="F27" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="G27" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="H27" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I27" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J27" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K27" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L27" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="M27" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="N27" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="O27" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="P27" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="Q27" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B28" t="str">
         <f t="shared" si="11"/>
         <v>差分なし</v>
       </c>
-      <c r="C26" s="5" t="str">
-        <f t="shared" ref="C26:Q26" si="13">IF(AND(C20="",C23=""),"",EXACT(C20,C23))</f>
-        <v/>
-      </c>
-      <c r="D26" s="5" t="str">
+      <c r="C28" s="5" t="str">
+        <f t="shared" ref="C28:Q28" si="13">IF(AND(C22="",C25=""),"",EXACT(C22,C25))</f>
+        <v/>
+      </c>
+      <c r="D28" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="E26" s="5" t="str">
+      <c r="E28" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="F26" s="5" t="str">
+      <c r="F28" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="G26" s="5" t="str">
+      <c r="G28" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="H26" s="5" t="str">
+      <c r="H28" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="I26" s="5" t="str">
+      <c r="I28" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="J26" s="5" t="str">
+      <c r="J28" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="K26" s="5" t="str">
+      <c r="K28" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="L26" s="5" t="str">
+      <c r="L28" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="M26" s="5" t="str">
+      <c r="M28" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N26" s="5" t="str">
+      <c r="N28" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="O26" s="5" t="str">
+      <c r="O28" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="P26" s="5" t="str">
+      <c r="P28" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="Q26" s="5" t="str">
+      <c r="Q28" s="5" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17" ht="18.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" s="19" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="2:17" ht="18.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30">
-        <f>C29-C28</f>
+      <c r="C32">
+        <f>C31-C30</f>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
-      <c r="P32" s="2"/>
-      <c r="Q32" s="2"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B33" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" s="4" t="b">
-        <f t="shared" ref="C33:Q33" si="14">EXACT(C5,C18)</f>
+    <row r="34" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B35" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="D33" s="4" t="b">
+      <c r="C35" s="4" t="b">
+        <f t="shared" ref="C35:Q35" si="14">EXACT(C6,C20)</f>
+        <v>0</v>
+      </c>
+      <c r="D35" s="4" t="b">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="E33" s="4" t="b">
+      <c r="E35" s="4" t="b">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="F33" s="4" t="b">
+      <c r="F35" s="4" t="b">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="G33" s="4" t="b">
+      <c r="G35" s="4" t="b">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="H33" s="4" t="b">
+      <c r="H35" s="4" t="b">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="I33" s="4" t="b">
+      <c r="I35" s="4" t="b">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="J33" s="4" t="b">
+      <c r="J35" s="4" t="b">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="K33" s="4" t="b">
+      <c r="K35" s="4" t="b">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="L33" s="4" t="b">
+      <c r="L35" s="4" t="b">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="M33" s="4" t="b">
+      <c r="M35" s="4" t="b">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="N33" s="4" t="b">
+      <c r="N35" s="4" t="b">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="O33" s="4" t="b">
+      <c r="O35" s="4" t="b">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="P33" s="4" t="b">
+      <c r="P35" s="4" t="b">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="Q33" s="4" t="b">
+      <c r="Q35" s="4" t="b">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B34" s="25"/>
-      <c r="C34" s="4" t="b">
-        <f t="shared" ref="C34:Q34" si="15">EXACT(C6,C19)</f>
-        <v>1</v>
-      </c>
-      <c r="D34" s="4" t="b">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B36" s="25"/>
+      <c r="C36" s="4" t="b">
+        <f t="shared" ref="C36:Q36" si="15">EXACT(C7,C21)</f>
+        <v>1</v>
+      </c>
+      <c r="D36" s="4" t="b">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="E34" s="4" t="b">
+      <c r="E36" s="4" t="b">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="F34" s="4" t="b">
+      <c r="F36" s="4" t="b">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="G34" s="4" t="b">
+      <c r="G36" s="4" t="b">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="H34" s="4" t="b">
+      <c r="H36" s="4" t="b">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="I34" s="4" t="b">
+      <c r="I36" s="4" t="b">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="J34" s="4" t="b">
+      <c r="J36" s="4" t="b">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="K34" s="4" t="b">
+      <c r="K36" s="4" t="b">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="L34" s="4" t="b">
+      <c r="L36" s="4" t="b">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="M34" s="4" t="b">
+      <c r="M36" s="4" t="b">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="N34" s="4" t="b">
+      <c r="N36" s="4" t="b">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="O34" s="4" t="b">
+      <c r="O36" s="4" t="b">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="P34" s="4" t="b">
+      <c r="P36" s="4" t="b">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
-      <c r="Q34" s="4" t="b">
+      <c r="Q36" s="4" t="b">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="26"/>
-      <c r="C35" s="4" t="b">
-        <f t="shared" ref="C35:Q35" si="16">EXACT(C7,C20)</f>
-        <v>1</v>
-      </c>
-      <c r="D35" s="4" t="b">
+    <row r="37" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="26"/>
+      <c r="C37" s="4" t="b">
+        <f t="shared" ref="C37:Q37" si="16">EXACT(C8,C22)</f>
+        <v>1</v>
+      </c>
+      <c r="D37" s="4" t="b">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="E35" s="4" t="b">
+      <c r="E37" s="4" t="b">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="F35" s="4" t="b">
+      <c r="F37" s="4" t="b">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="G35" s="4" t="b">
+      <c r="G37" s="4" t="b">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="H35" s="4" t="b">
+      <c r="H37" s="4" t="b">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="I35" s="4" t="b">
+      <c r="I37" s="4" t="b">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="J35" s="4" t="b">
+      <c r="J37" s="4" t="b">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="K35" s="4" t="b">
+      <c r="K37" s="4" t="b">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="L35" s="4" t="b">
+      <c r="L37" s="4" t="b">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="M35" s="4" t="b">
+      <c r="M37" s="4" t="b">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="N35" s="4" t="b">
+      <c r="N37" s="4" t="b">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="O35" s="4" t="b">
+      <c r="O37" s="4" t="b">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="P35" s="4" t="b">
+      <c r="P37" s="4" t="b">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="Q35" s="4" t="b">
+      <c r="Q37" s="4" t="b">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B36" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="4" t="b">
-        <f t="shared" ref="C36:Q36" si="17">EXACT(C8,C21)</f>
-        <v>1</v>
-      </c>
-      <c r="D36" s="4" t="b">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B38" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" s="4" t="b">
+        <f t="shared" ref="C38:Q38" si="17">EXACT(C9,C23)</f>
+        <v>1</v>
+      </c>
+      <c r="D38" s="4" t="b">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="E36" s="4" t="b">
+      <c r="E38" s="4" t="b">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="F36" s="4" t="b">
+      <c r="F38" s="4" t="b">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="G36" s="4" t="b">
+      <c r="G38" s="4" t="b">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="H36" s="4" t="b">
+      <c r="H38" s="4" t="b">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="I36" s="4" t="b">
+      <c r="I38" s="4" t="b">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="J36" s="4" t="b">
+      <c r="J38" s="4" t="b">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="K36" s="4" t="b">
+      <c r="K38" s="4" t="b">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="L36" s="4" t="b">
+      <c r="L38" s="4" t="b">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="M36" s="4" t="b">
+      <c r="M38" s="4" t="b">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="N36" s="4" t="b">
+      <c r="N38" s="4" t="b">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="O36" s="4" t="b">
+      <c r="O38" s="4" t="b">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="P36" s="4" t="b">
+      <c r="P38" s="4" t="b">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="Q36" s="4" t="b">
+      <c r="Q38" s="4" t="b">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B37" s="22"/>
-      <c r="C37" s="4" t="b">
-        <f t="shared" ref="C37:Q37" si="18">EXACT(C9,C22)</f>
-        <v>1</v>
-      </c>
-      <c r="D37" s="4" t="b">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B39" s="22"/>
+      <c r="C39" s="4" t="b">
+        <f t="shared" ref="C39:Q39" si="18">EXACT(C10,C24)</f>
+        <v>1</v>
+      </c>
+      <c r="D39" s="4" t="b">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
-      <c r="E37" s="4" t="b">
+      <c r="E39" s="4" t="b">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
-      <c r="F37" s="4" t="b">
+      <c r="F39" s="4" t="b">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
-      <c r="G37" s="4" t="b">
+      <c r="G39" s="4" t="b">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
-      <c r="H37" s="4" t="b">
+      <c r="H39" s="4" t="b">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
-      <c r="I37" s="4" t="b">
+      <c r="I39" s="4" t="b">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
-      <c r="J37" s="4" t="b">
+      <c r="J39" s="4" t="b">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
-      <c r="K37" s="4" t="b">
+      <c r="K39" s="4" t="b">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
-      <c r="L37" s="4" t="b">
+      <c r="L39" s="4" t="b">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
-      <c r="M37" s="4" t="b">
+      <c r="M39" s="4" t="b">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
-      <c r="N37" s="4" t="b">
+      <c r="N39" s="4" t="b">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
-      <c r="O37" s="4" t="b">
+      <c r="O39" s="4" t="b">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
-      <c r="P37" s="4" t="b">
+      <c r="P39" s="4" t="b">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
-      <c r="Q37" s="4" t="b">
+      <c r="Q39" s="4" t="b">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="23"/>
-      <c r="C38" s="4" t="b">
-        <f t="shared" ref="C38:Q38" si="19">EXACT(C10,C23)</f>
-        <v>1</v>
-      </c>
-      <c r="D38" s="4" t="b">
+    <row r="40" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="23"/>
+      <c r="C40" s="4" t="b">
+        <f t="shared" ref="C40:Q40" si="19">EXACT(C11,C25)</f>
+        <v>1</v>
+      </c>
+      <c r="D40" s="4" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="E38" s="4" t="b">
+      <c r="E40" s="4" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="F38" s="4" t="b">
+      <c r="F40" s="4" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="G38" s="4" t="b">
+      <c r="G40" s="4" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="H38" s="4" t="b">
+      <c r="H40" s="4" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="I38" s="4" t="b">
+      <c r="I40" s="4" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="J38" s="4" t="b">
+      <c r="J40" s="4" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="K38" s="4" t="b">
+      <c r="K40" s="4" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="L38" s="4" t="b">
+      <c r="L40" s="4" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="M38" s="4" t="b">
+      <c r="M40" s="4" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="N38" s="4" t="b">
+      <c r="N40" s="4" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="O38" s="4" t="b">
+      <c r="O40" s="4" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="P38" s="4" t="b">
+      <c r="P40" s="4" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="Q38" s="4" t="b">
+      <c r="Q40" s="4" t="b">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="B35:B37"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="C30">
+  <conditionalFormatting sqref="C32">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="notEqual">
       <formula>0</formula>
     </cfRule>
@@ -2192,7 +2203,7 @@
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="5" operator="containsText" id="{CAD14AC2-62CE-43F2-B4AA-F9BFEB933488}">
-            <xm:f>NOT(ISERROR(SEARCH(TRUE,A11)))</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(TRUE,A12)))</xm:f>
             <xm:f>TRUE</xm:f>
             <x14:dxf>
               <fill>
@@ -2203,7 +2214,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="containsText" priority="6" operator="containsText" id="{1D0FCC6B-C06B-4364-910E-BEE1D3BFB1FB}">
-            <xm:f>NOT(ISERROR(SEARCH(FALSE,A11)))</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(FALSE,A12)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
               <font>
@@ -2216,11 +2227,11 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A11:XFD13</xm:sqref>
+          <xm:sqref>A12:XFD14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="3" operator="containsText" id="{1AAA626F-0B1B-493D-B032-2439B76BA3CF}">
-            <xm:f>NOT(ISERROR(SEARCH(TRUE,A24)))</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(TRUE,A26)))</xm:f>
             <xm:f>TRUE</xm:f>
             <x14:dxf>
               <fill>
@@ -2231,7 +2242,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="containsText" priority="4" operator="containsText" id="{4AF720BF-5075-45A6-A62B-5D24F02125E8}">
-            <xm:f>NOT(ISERROR(SEARCH(FALSE,A24)))</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(FALSE,A26)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
               <font>
@@ -2244,11 +2255,11 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A24:XFD26</xm:sqref>
+          <xm:sqref>A26:XFD28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="7" operator="containsText" id="{5C3A0888-82EE-415E-B62D-DDB3E0ECE325}">
-            <xm:f>NOT(ISERROR(SEARCH(FALSE,A33)))</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(FALSE,A35)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
               <font>
@@ -2262,7 +2273,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="containsText" priority="8" operator="containsText" id="{BA07F738-C788-4E99-87A1-1EF9C7E6D3CD}">
-            <xm:f>NOT(ISERROR(SEARCH(TRUE,A33)))</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(TRUE,A35)))</xm:f>
             <xm:f>TRUE</xm:f>
             <x14:dxf>
               <fill>
@@ -2272,7 +2283,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A33:XFD38</xm:sqref>
+          <xm:sqref>A35:XFD40</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -2291,24 +2302,24 @@
   <sheetData>
     <row r="1" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
         <v>12</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="18.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
